--- a/ig/DM-AVRIL-2026/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
+++ b/ig/DM-AVRIL-2026/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260330120000</t>
+    <t>20260505120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T12:00:00+01:00</t>
+    <t>2026-05-05T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1842,7 +1842,7 @@
     <t>0538</t>
   </si>
   <si>
-    <t>Thérapie de groupe ou atelier à médiation orale et-ou écrite (groupe de parole, d'écriture)</t>
+    <t>Thérapie de groupe ou atelier à médiation orale et/ou écrite (groupe de parole, d'écriture)</t>
   </si>
   <si>
     <t>0539</t>
@@ -4134,7 +4134,7 @@
     <t>1014</t>
   </si>
   <si>
-    <t>Fourniture de matériel d'hygiène, de prévention et de RdRD</t>
+    <t>Fourniture de matériel d’hygiène, de prévention et de Réduction des Risques et des Dommages (RdRD)</t>
   </si>
   <si>
     <t>1015</t>
@@ -6624,7 +6624,7 @@
     <t>1453</t>
   </si>
   <si>
-    <t>Suivi, repérage précoce et accompagnement du développement psychomoteur, des troubles de comportement et des Troubles Neuro Développementaux</t>
+    <t>Suivi, repérage précoce et accompagnement du développement psychomoteur, des troubles de comportement et des Troubles Neuro Développementaux</t>
   </si>
   <si>
     <t>1454</t>
